--- a/artfynd/A 46196-2025 artfynd.xlsx
+++ b/artfynd/A 46196-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129472663</v>
       </c>
       <c r="B2" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,49 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129472653</v>
+        <v>129472633</v>
       </c>
       <c r="B3" t="n">
-        <v>98710</v>
+        <v>57724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>740803</v>
+        <v>740790</v>
       </c>
       <c r="R3" t="n">
-        <v>7126041</v>
+        <v>7126015</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,7 +851,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -874,45 +869,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129472633</v>
+        <v>129472653</v>
       </c>
       <c r="B4" t="n">
-        <v>57724</v>
+        <v>98712</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>740790</v>
+        <v>740803</v>
       </c>
       <c r="R4" t="n">
-        <v>7126015</v>
+        <v>7126041</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -953,6 +952,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1168,7 +1168,7 @@
         <v>129472654</v>
       </c>
       <c r="B7" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,49 +1267,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129472657</v>
+        <v>129472660</v>
       </c>
       <c r="B8" t="n">
-        <v>98710</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>740885</v>
+        <v>740736</v>
       </c>
       <c r="R8" t="n">
-        <v>7126212</v>
+        <v>7126051</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1350,7 +1346,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1369,45 +1364,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129472660</v>
+        <v>129472657</v>
       </c>
       <c r="B9" t="n">
-        <v>79043</v>
+        <v>98712</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>740736</v>
+        <v>740885</v>
       </c>
       <c r="R9" t="n">
-        <v>7126051</v>
+        <v>7126212</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1448,6 +1447,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1469,7 +1469,7 @@
         <v>129472655</v>
       </c>
       <c r="B10" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>129472648</v>
       </c>
       <c r="B11" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>129472661</v>
       </c>
       <c r="B12" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>129472662</v>
       </c>
       <c r="B14" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 46196-2025 artfynd.xlsx
+++ b/artfynd/A 46196-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>129472653</v>
       </c>
       <c r="B4" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>129472654</v>
       </c>
       <c r="B7" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>129472657</v>
       </c>
       <c r="B9" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>129472655</v>
       </c>
       <c r="B10" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1568,10 +1568,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129472648</v>
+        <v>129472661</v>
       </c>
       <c r="B11" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1579,37 +1579,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>740721</v>
+        <v>740730</v>
       </c>
       <c r="R11" t="n">
-        <v>7126084</v>
+        <v>7126018</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1650,7 +1647,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1669,10 +1665,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129472661</v>
+        <v>129472648</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1680,34 +1676,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>740730</v>
+        <v>740721</v>
       </c>
       <c r="R12" t="n">
-        <v>7126018</v>
+        <v>7126084</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1748,6 +1747,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 46196-2025 artfynd.xlsx
+++ b/artfynd/A 46196-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>129472653</v>
       </c>
       <c r="B4" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>129472654</v>
       </c>
       <c r="B7" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,45 +1267,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129472660</v>
+        <v>129472657</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>740736</v>
+        <v>740885</v>
       </c>
       <c r="R8" t="n">
-        <v>7126051</v>
+        <v>7126212</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1346,6 +1350,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1364,49 +1369,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129472657</v>
+        <v>129472660</v>
       </c>
       <c r="B9" t="n">
-        <v>98716</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>740885</v>
+        <v>740736</v>
       </c>
       <c r="R9" t="n">
-        <v>7126212</v>
+        <v>7126051</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1447,7 +1448,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1469,7 +1469,7 @@
         <v>129472655</v>
       </c>
       <c r="B10" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1568,10 +1568,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129472661</v>
+        <v>129472648</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1579,34 +1579,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>740730</v>
+        <v>740721</v>
       </c>
       <c r="R11" t="n">
-        <v>7126018</v>
+        <v>7126084</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1647,6 +1650,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1665,10 +1669,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129472648</v>
+        <v>129472661</v>
       </c>
       <c r="B12" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,37 +1680,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>740721</v>
+        <v>740730</v>
       </c>
       <c r="R12" t="n">
-        <v>7126084</v>
+        <v>7126018</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1747,7 +1748,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 46196-2025 artfynd.xlsx
+++ b/artfynd/A 46196-2025 artfynd.xlsx
@@ -1267,49 +1267,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129472657</v>
+        <v>129472660</v>
       </c>
       <c r="B8" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>740885</v>
+        <v>740736</v>
       </c>
       <c r="R8" t="n">
-        <v>7126212</v>
+        <v>7126051</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1350,7 +1346,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1369,45 +1364,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129472660</v>
+        <v>129472657</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>740736</v>
+        <v>740885</v>
       </c>
       <c r="R9" t="n">
-        <v>7126051</v>
+        <v>7126212</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1448,6 +1447,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 46196-2025 artfynd.xlsx
+++ b/artfynd/A 46196-2025 artfynd.xlsx
@@ -1267,45 +1267,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129472660</v>
+        <v>129472657</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>740736</v>
+        <v>740885</v>
       </c>
       <c r="R8" t="n">
-        <v>7126051</v>
+        <v>7126212</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1346,6 +1350,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1364,49 +1369,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129472657</v>
+        <v>129472660</v>
       </c>
       <c r="B9" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>740885</v>
+        <v>740736</v>
       </c>
       <c r="R9" t="n">
-        <v>7126212</v>
+        <v>7126051</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1447,7 +1448,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 46196-2025 artfynd.xlsx
+++ b/artfynd/A 46196-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>129472653</v>
       </c>
       <c r="B4" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>129472654</v>
       </c>
       <c r="B7" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,49 +1267,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129472657</v>
+        <v>129472660</v>
       </c>
       <c r="B8" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>740885</v>
+        <v>740736</v>
       </c>
       <c r="R8" t="n">
-        <v>7126212</v>
+        <v>7126051</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1350,7 +1346,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1369,45 +1364,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129472660</v>
+        <v>129472657</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>740736</v>
+        <v>740885</v>
       </c>
       <c r="R9" t="n">
-        <v>7126051</v>
+        <v>7126212</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1448,6 +1447,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1469,7 +1469,7 @@
         <v>129472655</v>
       </c>
       <c r="B10" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 46196-2025 artfynd.xlsx
+++ b/artfynd/A 46196-2025 artfynd.xlsx
@@ -1568,10 +1568,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129472648</v>
+        <v>129472661</v>
       </c>
       <c r="B11" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1579,37 +1579,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>740721</v>
+        <v>740730</v>
       </c>
       <c r="R11" t="n">
-        <v>7126084</v>
+        <v>7126018</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1650,7 +1647,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1669,10 +1665,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129472661</v>
+        <v>129472648</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1680,34 +1676,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>740730</v>
+        <v>740721</v>
       </c>
       <c r="R12" t="n">
-        <v>7126018</v>
+        <v>7126084</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1748,6 +1747,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 46196-2025 artfynd.xlsx
+++ b/artfynd/A 46196-2025 artfynd.xlsx
@@ -1568,10 +1568,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129472661</v>
+        <v>129472648</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1579,34 +1579,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>740730</v>
+        <v>740721</v>
       </c>
       <c r="R11" t="n">
-        <v>7126018</v>
+        <v>7126084</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1647,6 +1650,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1665,10 +1669,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129472648</v>
+        <v>129472661</v>
       </c>
       <c r="B12" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,37 +1680,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>740721</v>
+        <v>740730</v>
       </c>
       <c r="R12" t="n">
-        <v>7126084</v>
+        <v>7126018</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1747,7 +1748,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 46196-2025 artfynd.xlsx
+++ b/artfynd/A 46196-2025 artfynd.xlsx
@@ -772,45 +772,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129472633</v>
+        <v>129472653</v>
       </c>
       <c r="B3" t="n">
-        <v>57724</v>
+        <v>98727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>740790</v>
+        <v>740803</v>
       </c>
       <c r="R3" t="n">
-        <v>7126015</v>
+        <v>7126041</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,6 +855,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -869,49 +874,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129472653</v>
+        <v>129472633</v>
       </c>
       <c r="B4" t="n">
-        <v>98727</v>
+        <v>57724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>740803</v>
+        <v>740790</v>
       </c>
       <c r="R4" t="n">
-        <v>7126041</v>
+        <v>7126015</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,7 +953,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 46196-2025 artfynd.xlsx
+++ b/artfynd/A 46196-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129472663</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,49 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129472653</v>
+        <v>129472633</v>
       </c>
       <c r="B3" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>740803</v>
+        <v>740790</v>
       </c>
       <c r="R3" t="n">
-        <v>7126041</v>
+        <v>7126015</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,7 +851,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -874,45 +869,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129472633</v>
+        <v>129472653</v>
       </c>
       <c r="B4" t="n">
-        <v>57724</v>
+        <v>98756</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>740790</v>
+        <v>740803</v>
       </c>
       <c r="R4" t="n">
-        <v>7126015</v>
+        <v>7126041</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -953,6 +952,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -974,7 +974,7 @@
         <v>129472627</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>129463348</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>129472654</v>
       </c>
       <c r="B7" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>129472660</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>129472657</v>
       </c>
       <c r="B9" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>129472655</v>
       </c>
       <c r="B10" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>129472648</v>
       </c>
       <c r="B11" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>129472661</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>129464387</v>
       </c>
       <c r="B13" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>129472662</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 46196-2025 artfynd.xlsx
+++ b/artfynd/A 46196-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129472663</v>
       </c>
       <c r="B2" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,45 +772,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129472633</v>
+        <v>129472653</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>98768</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>740790</v>
+        <v>740803</v>
       </c>
       <c r="R3" t="n">
-        <v>7126015</v>
+        <v>7126041</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,6 +855,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -869,49 +874,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129472653</v>
+        <v>129472633</v>
       </c>
       <c r="B4" t="n">
-        <v>98756</v>
+        <v>57732</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>740803</v>
+        <v>740790</v>
       </c>
       <c r="R4" t="n">
-        <v>7126041</v>
+        <v>7126015</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,7 +953,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -974,7 +974,7 @@
         <v>129472627</v>
       </c>
       <c r="B5" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>129463348</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>129472654</v>
       </c>
       <c r="B7" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>129472660</v>
       </c>
       <c r="B8" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>129472657</v>
       </c>
       <c r="B9" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>129472655</v>
       </c>
       <c r="B10" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>129472648</v>
       </c>
       <c r="B11" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>129472661</v>
       </c>
       <c r="B12" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>129464387</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>129472662</v>
       </c>
       <c r="B14" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 46196-2025 artfynd.xlsx
+++ b/artfynd/A 46196-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129472663</v>
       </c>
       <c r="B2" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,49 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129472653</v>
+        <v>129472633</v>
       </c>
       <c r="B3" t="n">
-        <v>98768</v>
+        <v>57733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>740803</v>
+        <v>740790</v>
       </c>
       <c r="R3" t="n">
-        <v>7126041</v>
+        <v>7126015</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,7 +851,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -874,45 +869,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129472633</v>
+        <v>129472653</v>
       </c>
       <c r="B4" t="n">
-        <v>57732</v>
+        <v>98769</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>740790</v>
+        <v>740803</v>
       </c>
       <c r="R4" t="n">
-        <v>7126015</v>
+        <v>7126041</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -953,6 +952,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -974,7 +974,7 @@
         <v>129472627</v>
       </c>
       <c r="B5" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>129463348</v>
       </c>
       <c r="B6" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>129472654</v>
       </c>
       <c r="B7" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>129472660</v>
       </c>
       <c r="B8" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>129472657</v>
       </c>
       <c r="B9" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>129472655</v>
       </c>
       <c r="B10" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1568,10 +1568,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129472648</v>
+        <v>129472661</v>
       </c>
       <c r="B11" t="n">
-        <v>80180</v>
+        <v>79076</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1579,37 +1579,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>740721</v>
+        <v>740730</v>
       </c>
       <c r="R11" t="n">
-        <v>7126084</v>
+        <v>7126018</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1650,7 +1647,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1669,10 +1665,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129472661</v>
+        <v>129472648</v>
       </c>
       <c r="B12" t="n">
-        <v>79075</v>
+        <v>80181</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1680,34 +1676,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>740730</v>
+        <v>740721</v>
       </c>
       <c r="R12" t="n">
-        <v>7126018</v>
+        <v>7126084</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1748,6 +1747,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1769,7 +1769,7 @@
         <v>129464387</v>
       </c>
       <c r="B13" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>129472662</v>
       </c>
       <c r="B14" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 46196-2025 artfynd.xlsx
+++ b/artfynd/A 46196-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129472663</v>
       </c>
       <c r="B2" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129472653</v>
       </c>
       <c r="B4" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>129472654</v>
       </c>
       <c r="B7" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>129472660</v>
       </c>
       <c r="B8" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>129472657</v>
       </c>
       <c r="B9" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>129472655</v>
       </c>
       <c r="B10" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1568,10 +1568,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129472661</v>
+        <v>129472648</v>
       </c>
       <c r="B11" t="n">
-        <v>79076</v>
+        <v>80186</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1579,34 +1579,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>740730</v>
+        <v>740721</v>
       </c>
       <c r="R11" t="n">
-        <v>7126018</v>
+        <v>7126084</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1647,6 +1650,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1665,10 +1669,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129472648</v>
+        <v>129472661</v>
       </c>
       <c r="B12" t="n">
-        <v>80181</v>
+        <v>79081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,37 +1680,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>740721</v>
+        <v>740730</v>
       </c>
       <c r="R12" t="n">
-        <v>7126084</v>
+        <v>7126018</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1747,7 +1748,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1866,7 +1866,7 @@
         <v>129472662</v>
       </c>
       <c r="B14" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 46196-2025 artfynd.xlsx
+++ b/artfynd/A 46196-2025 artfynd.xlsx
@@ -1568,10 +1568,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129472648</v>
+        <v>129472661</v>
       </c>
       <c r="B11" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1579,37 +1579,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>740721</v>
+        <v>740730</v>
       </c>
       <c r="R11" t="n">
-        <v>7126084</v>
+        <v>7126018</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1650,7 +1647,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1669,10 +1665,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129472661</v>
+        <v>129472648</v>
       </c>
       <c r="B12" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1680,34 +1676,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>740730</v>
+        <v>740721</v>
       </c>
       <c r="R12" t="n">
-        <v>7126018</v>
+        <v>7126084</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1748,6 +1747,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 46196-2025 artfynd.xlsx
+++ b/artfynd/A 46196-2025 artfynd.xlsx
@@ -772,45 +772,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129472633</v>
+        <v>129472653</v>
       </c>
       <c r="B3" t="n">
-        <v>57733</v>
+        <v>98778</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>740790</v>
+        <v>740803</v>
       </c>
       <c r="R3" t="n">
-        <v>7126015</v>
+        <v>7126041</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,6 +855,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -869,49 +874,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129472653</v>
+        <v>129472633</v>
       </c>
       <c r="B4" t="n">
-        <v>98774</v>
+        <v>57733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>740803</v>
+        <v>740790</v>
       </c>
       <c r="R4" t="n">
-        <v>7126041</v>
+        <v>7126015</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,7 +953,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1168,7 +1168,7 @@
         <v>129472654</v>
       </c>
       <c r="B7" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,45 +1267,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129472660</v>
+        <v>129472657</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>98778</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>740736</v>
+        <v>740885</v>
       </c>
       <c r="R8" t="n">
-        <v>7126051</v>
+        <v>7126212</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1346,6 +1350,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1364,49 +1369,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129472657</v>
+        <v>129472660</v>
       </c>
       <c r="B9" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>740885</v>
+        <v>740736</v>
       </c>
       <c r="R9" t="n">
-        <v>7126212</v>
+        <v>7126051</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1447,7 +1448,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1469,7 +1469,7 @@
         <v>129472655</v>
       </c>
       <c r="B10" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1568,10 +1568,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129472661</v>
+        <v>129472648</v>
       </c>
       <c r="B11" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1579,34 +1579,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>740730</v>
+        <v>740721</v>
       </c>
       <c r="R11" t="n">
-        <v>7126018</v>
+        <v>7126084</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1647,6 +1650,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1665,10 +1669,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129472648</v>
+        <v>129472661</v>
       </c>
       <c r="B12" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,37 +1680,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>740721</v>
+        <v>740730</v>
       </c>
       <c r="R12" t="n">
-        <v>7126084</v>
+        <v>7126018</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1747,7 +1748,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 46196-2025 artfynd.xlsx
+++ b/artfynd/A 46196-2025 artfynd.xlsx
@@ -772,49 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129472653</v>
+        <v>129472633</v>
       </c>
       <c r="B3" t="n">
-        <v>98778</v>
+        <v>57733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>740803</v>
+        <v>740790</v>
       </c>
       <c r="R3" t="n">
-        <v>7126041</v>
+        <v>7126015</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,7 +851,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -874,45 +869,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129472633</v>
+        <v>129472653</v>
       </c>
       <c r="B4" t="n">
-        <v>57733</v>
+        <v>98780</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>740790</v>
+        <v>740803</v>
       </c>
       <c r="R4" t="n">
-        <v>7126015</v>
+        <v>7126041</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -953,6 +952,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1168,7 +1168,7 @@
         <v>129472654</v>
       </c>
       <c r="B7" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>129472657</v>
       </c>
       <c r="B8" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>129472655</v>
       </c>
       <c r="B10" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1568,10 +1568,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129472648</v>
+        <v>129472661</v>
       </c>
       <c r="B11" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1579,37 +1579,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>740721</v>
+        <v>740730</v>
       </c>
       <c r="R11" t="n">
-        <v>7126084</v>
+        <v>7126018</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1650,7 +1647,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1669,10 +1665,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129472661</v>
+        <v>129472648</v>
       </c>
       <c r="B12" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1680,34 +1676,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>740730</v>
+        <v>740721</v>
       </c>
       <c r="R12" t="n">
-        <v>7126018</v>
+        <v>7126084</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1748,6 +1747,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 46196-2025 artfynd.xlsx
+++ b/artfynd/A 46196-2025 artfynd.xlsx
@@ -1267,49 +1267,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129472657</v>
+        <v>129472660</v>
       </c>
       <c r="B8" t="n">
-        <v>98780</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>740885</v>
+        <v>740736</v>
       </c>
       <c r="R8" t="n">
-        <v>7126212</v>
+        <v>7126051</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1350,7 +1346,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1369,45 +1364,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129472660</v>
+        <v>129472657</v>
       </c>
       <c r="B9" t="n">
-        <v>79081</v>
+        <v>98780</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>740736</v>
+        <v>740885</v>
       </c>
       <c r="R9" t="n">
-        <v>7126051</v>
+        <v>7126212</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1448,6 +1447,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 46196-2025 artfynd.xlsx
+++ b/artfynd/A 46196-2025 artfynd.xlsx
@@ -1267,45 +1267,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129472660</v>
+        <v>129472657</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>98780</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>740736</v>
+        <v>740885</v>
       </c>
       <c r="R8" t="n">
-        <v>7126051</v>
+        <v>7126212</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1346,6 +1350,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1364,49 +1369,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129472657</v>
+        <v>129472660</v>
       </c>
       <c r="B9" t="n">
-        <v>98780</v>
+        <v>79081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>740885</v>
+        <v>740736</v>
       </c>
       <c r="R9" t="n">
-        <v>7126212</v>
+        <v>7126051</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1447,7 +1448,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
